--- a/01_Input/00_CO Validation/Mexico - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Mexico - Energy Projects.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27002"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27016"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edgar.gonzalez\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="149" documentId="8_{F2D2D00D-A89C-0A4B-9B24-C268CBE6EBDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{495F9872-D957-4C70-A02A-F543CF46129F}"/>
+  <xr:revisionPtr revIDLastSave="156" documentId="8_{F2D2D00D-A89C-0A4B-9B24-C268CBE6EBDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF764058-9EF8-4E0C-8FA6-AD97307D1E37}"/>
   <bookViews>
     <workbookView xWindow="2685" yWindow="2685" windowWidth="21600" windowHeight="11175" xr2:uid="{FE1040E1-1AC7-44EE-934B-383420C1C5D8}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="68">
   <si>
     <t>Project ID</t>
   </si>
@@ -195,6 +195,9 @@
   </si>
   <si>
     <t>indirect beneficiaries (154 (99 women, 55 men)</t>
+  </si>
+  <si>
+    <t>Transport Services</t>
   </si>
   <si>
     <t>Planning project to asset the pontential of technological tranistion in motor taxis to implemtn electric motors in Uman, Yucatán.</t>
@@ -346,7 +349,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -393,12 +396,106 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -451,12 +548,75 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -477,27 +637,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -824,13 +963,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="24" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="9" t="s">
@@ -851,7 +990,7 @@
       <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="36" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="17" t="s">
@@ -883,16 +1022,16 @@
       </c>
     </row>
     <row r="2" spans="1:19" ht="183" customHeight="1">
-      <c r="A2" s="30">
+      <c r="A2" s="25">
         <v>122398</v>
       </c>
       <c r="B2" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="33" t="s">
+      <c r="C2" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="12">
+      <c r="D2" s="23">
         <v>50000</v>
       </c>
       <c r="E2" s="13" t="s">
@@ -907,16 +1046,16 @@
       <c r="H2" s="13">
         <v>163</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="34" t="s">
+      <c r="J2" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="K2" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="35" t="s">
+      <c r="L2" s="22" t="s">
         <v>27</v>
       </c>
       <c r="M2" s="14"/>
@@ -934,10 +1073,10 @@
       </c>
     </row>
     <row r="3" spans="1:19" ht="121.5">
-      <c r="A3" s="30"/>
-      <c r="B3" s="31"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="12">
+      <c r="A3" s="26"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="23">
         <v>50000</v>
       </c>
       <c r="E3" s="13" t="s">
@@ -950,14 +1089,14 @@
       <c r="H3" s="13">
         <v>30</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="34"/>
-      <c r="K3" s="15" t="s">
+      <c r="J3" s="38"/>
+      <c r="K3" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="L3" s="35"/>
+      <c r="L3" s="22"/>
       <c r="M3" s="14"/>
       <c r="N3" s="16" t="s">
         <v>28</v>
@@ -973,10 +1112,10 @@
       </c>
     </row>
     <row r="4" spans="1:19" ht="91.5">
-      <c r="A4" s="30"/>
-      <c r="B4" s="31"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="12">
+      <c r="A4" s="26"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="23">
         <v>4999</v>
       </c>
       <c r="E4" s="13" t="s">
@@ -989,14 +1128,14 @@
       <c r="H4" s="13">
         <v>77</v>
       </c>
-      <c r="I4" s="13" t="s">
+      <c r="I4" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="J4" s="34"/>
-      <c r="K4" s="15" t="s">
+      <c r="J4" s="38"/>
+      <c r="K4" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="L4" s="35"/>
+      <c r="L4" s="22"/>
       <c r="M4" s="14"/>
       <c r="N4" s="16" t="s">
         <v>28</v>
@@ -1010,10 +1149,10 @@
       <c r="S4" s="16"/>
     </row>
     <row r="5" spans="1:19" ht="76.5">
-      <c r="A5" s="30"/>
-      <c r="B5" s="31"/>
-      <c r="C5" s="32"/>
-      <c r="D5" s="12">
+      <c r="A5" s="26"/>
+      <c r="B5" s="32"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="23">
         <v>4990</v>
       </c>
       <c r="E5" s="13" t="s">
@@ -1026,14 +1165,14 @@
       <c r="H5" s="13">
         <v>110</v>
       </c>
-      <c r="I5" s="13" t="s">
+      <c r="I5" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="34"/>
-      <c r="K5" s="15" t="s">
+      <c r="J5" s="38"/>
+      <c r="K5" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="35"/>
+      <c r="L5" s="22"/>
       <c r="M5" s="14"/>
       <c r="N5" s="16" t="s">
         <v>28</v>
@@ -1047,10 +1186,10 @@
       <c r="S5" s="16"/>
     </row>
     <row r="6" spans="1:19" ht="106.5">
-      <c r="A6" s="30"/>
-      <c r="B6" s="31"/>
-      <c r="C6" s="32"/>
-      <c r="D6" s="12">
+      <c r="A6" s="26"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="23">
         <v>3992</v>
       </c>
       <c r="E6" s="13" t="s">
@@ -1063,14 +1202,14 @@
       <c r="H6" s="13">
         <v>402</v>
       </c>
-      <c r="I6" s="13" t="s">
+      <c r="I6" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="34"/>
-      <c r="K6" s="15" t="s">
+      <c r="J6" s="38"/>
+      <c r="K6" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="L6" s="35"/>
+      <c r="L6" s="22"/>
       <c r="M6" s="14"/>
       <c r="N6" s="16" t="s">
         <v>28</v>
@@ -1084,10 +1223,10 @@
       <c r="S6" s="16"/>
     </row>
     <row r="7" spans="1:19" ht="60.75">
-      <c r="A7" s="30"/>
-      <c r="B7" s="31"/>
-      <c r="C7" s="32"/>
-      <c r="D7" s="12">
+      <c r="A7" s="26"/>
+      <c r="B7" s="32"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="23">
         <v>4997</v>
       </c>
       <c r="E7" s="13" t="s">
@@ -1100,14 +1239,14 @@
       <c r="H7" s="13">
         <v>400</v>
       </c>
-      <c r="I7" s="13" t="s">
+      <c r="I7" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="J7" s="34"/>
-      <c r="K7" s="15" t="s">
+      <c r="J7" s="38"/>
+      <c r="K7" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="L7" s="35"/>
+      <c r="L7" s="22"/>
       <c r="M7" s="14"/>
       <c r="N7" s="16" t="s">
         <v>28</v>
@@ -1121,10 +1260,10 @@
       <c r="S7" s="16"/>
     </row>
     <row r="8" spans="1:19" ht="91.5">
-      <c r="A8" s="30"/>
-      <c r="B8" s="31"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="12">
+      <c r="A8" s="26"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="23">
         <v>50000</v>
       </c>
       <c r="E8" s="13" t="s">
@@ -1137,14 +1276,14 @@
       <c r="H8" s="13">
         <v>14</v>
       </c>
-      <c r="I8" s="13" t="s">
+      <c r="I8" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="J8" s="34"/>
-      <c r="K8" s="15" t="s">
+      <c r="J8" s="38"/>
+      <c r="K8" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="L8" s="35"/>
+      <c r="L8" s="22"/>
       <c r="M8" s="14"/>
       <c r="N8" s="16" t="s">
         <v>28</v>
@@ -1160,10 +1299,10 @@
       </c>
     </row>
     <row r="9" spans="1:19" ht="137.25">
-      <c r="A9" s="30"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="12">
+      <c r="A9" s="26"/>
+      <c r="B9" s="32"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="23">
         <v>50000</v>
       </c>
       <c r="E9" s="13" t="s">
@@ -1176,14 +1315,14 @@
       <c r="H9" s="13">
         <v>14</v>
       </c>
-      <c r="I9" s="13" t="s">
+      <c r="I9" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="J9" s="34"/>
-      <c r="K9" s="15" t="s">
+      <c r="J9" s="38"/>
+      <c r="K9" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="L9" s="35"/>
+      <c r="L9" s="22"/>
       <c r="M9" s="14"/>
       <c r="N9" s="16" t="s">
         <v>28</v>
@@ -1199,14 +1338,14 @@
       </c>
     </row>
     <row r="10" spans="1:19" ht="106.5">
-      <c r="A10" s="30"/>
-      <c r="B10" s="31"/>
-      <c r="C10" s="32"/>
-      <c r="D10" s="12">
+      <c r="A10" s="27"/>
+      <c r="B10" s="33"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="23">
         <v>4900</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="F10" s="19" t="s">
         <v>32</v>
@@ -1215,14 +1354,14 @@
       <c r="H10" s="13">
         <v>15</v>
       </c>
-      <c r="I10" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="J10" s="34"/>
-      <c r="K10" s="15" t="s">
+      <c r="I10" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="L10" s="35"/>
+      <c r="J10" s="39"/>
+      <c r="K10" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="L10" s="22"/>
       <c r="M10" s="14"/>
       <c r="N10" s="16" t="s">
         <v>28</v>
@@ -1332,13 +1471,13 @@
       </c>
     </row>
     <row r="2" spans="1:19" ht="183" customHeight="1">
-      <c r="A2" s="30">
+      <c r="A2" s="20">
         <v>122398</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="29"/>
+      <c r="C2" s="42"/>
       <c r="D2" s="12">
         <v>50000</v>
       </c>
@@ -1357,13 +1496,13 @@
       <c r="I2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="J2" s="41" t="s">
         <v>25</v>
       </c>
       <c r="K2" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="20" t="s">
+      <c r="L2" s="40" t="s">
         <v>27</v>
       </c>
       <c r="M2" s="14"/>
@@ -1381,9 +1520,9 @@
       <c r="S2" s="16"/>
     </row>
     <row r="3" spans="1:19" ht="121.5">
-      <c r="A3" s="30"/>
-      <c r="B3" s="31"/>
-      <c r="C3" s="29"/>
+      <c r="A3" s="20"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="42"/>
       <c r="D3" s="12">
         <v>50000</v>
       </c>
@@ -1400,11 +1539,11 @@
       <c r="I3" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="21"/>
+      <c r="J3" s="41"/>
       <c r="K3" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="L3" s="20"/>
+      <c r="L3" s="40"/>
       <c r="M3" s="14"/>
       <c r="N3" s="16" t="s">
         <v>36</v>
@@ -1420,9 +1559,9 @@
       <c r="S3" s="16"/>
     </row>
     <row r="4" spans="1:19" ht="91.5">
-      <c r="A4" s="30"/>
-      <c r="B4" s="31"/>
-      <c r="C4" s="29"/>
+      <c r="A4" s="20"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="42"/>
       <c r="D4" s="12">
         <v>4999</v>
       </c>
@@ -1439,11 +1578,11 @@
       <c r="I4" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="J4" s="21"/>
+      <c r="J4" s="41"/>
       <c r="K4" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="L4" s="20"/>
+      <c r="L4" s="40"/>
       <c r="M4" s="14"/>
       <c r="N4" s="16"/>
       <c r="O4" s="16" t="s">
@@ -1457,9 +1596,9 @@
       <c r="S4" s="16"/>
     </row>
     <row r="5" spans="1:19" ht="76.5">
-      <c r="A5" s="30"/>
-      <c r="B5" s="31"/>
-      <c r="C5" s="29"/>
+      <c r="A5" s="20"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="42"/>
       <c r="D5" s="12">
         <v>4990</v>
       </c>
@@ -1476,11 +1615,11 @@
       <c r="I5" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="21"/>
+      <c r="J5" s="41"/>
       <c r="K5" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="20"/>
+      <c r="L5" s="40"/>
       <c r="M5" s="14"/>
       <c r="N5" s="16"/>
       <c r="O5" s="16" t="s">
@@ -1494,9 +1633,9 @@
       <c r="S5" s="16"/>
     </row>
     <row r="6" spans="1:19" ht="106.5">
-      <c r="A6" s="30"/>
-      <c r="B6" s="31"/>
-      <c r="C6" s="29"/>
+      <c r="A6" s="20"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="42"/>
       <c r="D6" s="12">
         <v>3992</v>
       </c>
@@ -1513,11 +1652,11 @@
       <c r="I6" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="21"/>
+      <c r="J6" s="41"/>
       <c r="K6" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="L6" s="20"/>
+      <c r="L6" s="40"/>
       <c r="M6" s="14"/>
       <c r="N6" s="16"/>
       <c r="O6" s="16" t="s">
@@ -1531,9 +1670,9 @@
       <c r="S6" s="16"/>
     </row>
     <row r="7" spans="1:19" ht="60.75">
-      <c r="A7" s="30"/>
-      <c r="B7" s="31"/>
-      <c r="C7" s="29"/>
+      <c r="A7" s="20"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="42"/>
       <c r="D7" s="12">
         <v>4997</v>
       </c>
@@ -1550,11 +1689,11 @@
       <c r="I7" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J7" s="21"/>
+      <c r="J7" s="41"/>
       <c r="K7" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="L7" s="20"/>
+      <c r="L7" s="40"/>
       <c r="M7" s="14"/>
       <c r="N7" s="16"/>
       <c r="O7" s="16" t="s">
@@ -1568,9 +1707,9 @@
       <c r="S7" s="16"/>
     </row>
     <row r="8" spans="1:19" ht="91.5">
-      <c r="A8" s="30"/>
-      <c r="B8" s="31"/>
-      <c r="C8" s="29"/>
+      <c r="A8" s="20"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="42"/>
       <c r="D8" s="12">
         <v>50000</v>
       </c>
@@ -1587,11 +1726,11 @@
       <c r="I8" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="J8" s="21"/>
+      <c r="J8" s="41"/>
       <c r="K8" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="L8" s="20"/>
+      <c r="L8" s="40"/>
       <c r="M8" s="14"/>
       <c r="N8" s="16" t="s">
         <v>48</v>
@@ -1607,9 +1746,9 @@
       <c r="S8" s="16"/>
     </row>
     <row r="9" spans="1:19" ht="137.25">
-      <c r="A9" s="30"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="29"/>
+      <c r="A9" s="20"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="42"/>
       <c r="D9" s="12">
         <v>50000</v>
       </c>
@@ -1626,11 +1765,11 @@
       <c r="I9" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="J9" s="21"/>
+      <c r="J9" s="41"/>
       <c r="K9" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="L9" s="20"/>
+      <c r="L9" s="40"/>
       <c r="M9" s="14"/>
       <c r="N9" s="16" t="s">
         <v>51</v>
@@ -1646,9 +1785,9 @@
       <c r="S9" s="16"/>
     </row>
     <row r="10" spans="1:19" ht="106.5">
-      <c r="A10" s="30"/>
-      <c r="B10" s="31"/>
-      <c r="C10" s="29"/>
+      <c r="A10" s="20"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="42"/>
       <c r="D10" s="12">
         <v>4900</v>
       </c>
@@ -1663,13 +1802,13 @@
         <v>15</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="J10" s="21"/>
+        <v>53</v>
+      </c>
+      <c r="J10" s="41"/>
       <c r="K10" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="L10" s="20"/>
+        <v>54</v>
+      </c>
+      <c r="L10" s="40"/>
       <c r="M10" s="14"/>
       <c r="N10" s="16"/>
       <c r="O10" s="16" t="s">
@@ -1750,14 +1889,14 @@
         <v>9</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="183" customHeight="1">
-      <c r="A2" s="22">
+      <c r="A2" s="43">
         <v>122398</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="45" t="s">
         <v>19</v>
       </c>
       <c r="C2" s="3"/>
@@ -1767,49 +1906,49 @@
       <c r="E2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="26" t="s">
+      <c r="F2" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="26" t="s">
+      <c r="G2" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="26" t="s">
-        <v>55</v>
+      <c r="H2" s="47" t="s">
+        <v>56</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="J2" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="J2" s="49" t="s">
         <v>25</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="121.5">
-      <c r="A3" s="23"/>
-      <c r="B3" s="25"/>
+      <c r="A3" s="44"/>
+      <c r="B3" s="46"/>
       <c r="C3" s="3"/>
       <c r="D3" s="6">
         <v>50000</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27"/>
+        <v>59</v>
+      </c>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
       <c r="I3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="28"/>
+      <c r="J3" s="49"/>
       <c r="K3" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="91.5">
-      <c r="A4" s="23"/>
-      <c r="B4" s="25"/>
+      <c r="A4" s="44"/>
+      <c r="B4" s="46"/>
       <c r="C4" s="3"/>
       <c r="D4" s="6">
         <v>4999</v>
@@ -1817,20 +1956,20 @@
       <c r="E4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="27"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
       <c r="I4" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="J4" s="28"/>
+      <c r="J4" s="49"/>
       <c r="K4" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="76.5">
-      <c r="A5" s="23"/>
-      <c r="B5" s="25"/>
+      <c r="A5" s="44"/>
+      <c r="B5" s="46"/>
       <c r="C5" s="3"/>
       <c r="D5" s="6">
         <v>4990</v>
@@ -1838,20 +1977,20 @@
       <c r="E5" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="27"/>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
       <c r="I5" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="28"/>
+      <c r="J5" s="49"/>
       <c r="K5" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="106.5">
-      <c r="A6" s="23"/>
-      <c r="B6" s="25"/>
+      <c r="A6" s="44"/>
+      <c r="B6" s="46"/>
       <c r="C6" s="3"/>
       <c r="D6" s="6">
         <v>3992</v>
@@ -1859,20 +1998,20 @@
       <c r="E6" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27"/>
-      <c r="H6" s="27"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="48"/>
       <c r="I6" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="28"/>
+      <c r="J6" s="49"/>
       <c r="K6" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="60.75">
-      <c r="A7" s="23"/>
-      <c r="B7" s="25"/>
+      <c r="A7" s="44"/>
+      <c r="B7" s="46"/>
       <c r="C7" s="3"/>
       <c r="D7" s="6">
         <v>4997</v>
@@ -1880,20 +2019,20 @@
       <c r="E7" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="27"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="27"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
       <c r="I7" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="J7" s="28"/>
+      <c r="J7" s="49"/>
       <c r="K7" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="91.5">
-      <c r="A8" s="23"/>
-      <c r="B8" s="25"/>
+      <c r="A8" s="44"/>
+      <c r="B8" s="46"/>
       <c r="C8" s="3"/>
       <c r="D8" s="6">
         <v>50000</v>
@@ -1901,20 +2040,20 @@
       <c r="E8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="48"/>
       <c r="I8" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="J8" s="28"/>
+      <c r="J8" s="49"/>
       <c r="K8" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="137.25">
-      <c r="A9" s="23"/>
-      <c r="B9" s="25"/>
+      <c r="A9" s="44"/>
+      <c r="B9" s="46"/>
       <c r="C9" s="3"/>
       <c r="D9" s="6">
         <v>50000</v>
@@ -1922,20 +2061,20 @@
       <c r="E9" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="27"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
       <c r="I9" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="J9" s="28"/>
+      <c r="J9" s="49"/>
       <c r="K9" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="106.5">
-      <c r="A10" s="23"/>
-      <c r="B10" s="25"/>
+      <c r="A10" s="44"/>
+      <c r="B10" s="46"/>
       <c r="C10" s="3"/>
       <c r="D10" s="6">
         <v>4900</v>
@@ -1943,15 +2082,15 @@
       <c r="E10" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="27"/>
+      <c r="F10" s="48"/>
+      <c r="G10" s="48"/>
+      <c r="H10" s="48"/>
       <c r="I10" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="J10" s="28"/>
+        <v>53</v>
+      </c>
+      <c r="J10" s="49"/>
       <c r="K10" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/01_Input/00_CO Validation/Mexico - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Mexico - Energy Projects.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27016"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27226"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edgar.gonzalez\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="156" documentId="8_{F2D2D00D-A89C-0A4B-9B24-C268CBE6EBDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF764058-9EF8-4E0C-8FA6-AD97307D1E37}"/>
+  <xr:revisionPtr revIDLastSave="182" documentId="8_{F2D2D00D-A89C-0A4B-9B24-C268CBE6EBDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B4F09F7-6B93-41A4-96E8-93C2ECD02252}"/>
   <bookViews>
     <workbookView xWindow="2685" yWindow="2685" windowWidth="21600" windowHeight="11175" xr2:uid="{FE1040E1-1AC7-44EE-934B-383420C1C5D8}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Projects (3)" sheetId="3" r:id="rId1"/>
     <sheet name="Projects (2)" sheetId="2" r:id="rId2"/>
     <sheet name="Projects" sheetId="1" r:id="rId3"/>
+    <sheet name="Beneficiary Categories" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="111">
   <si>
     <t>Project ID</t>
   </si>
@@ -73,7 +74,7 @@
     <t>Gender (% female)</t>
   </si>
   <si>
-    <t>Category</t>
+    <t>VF or Non-VF</t>
   </si>
   <si>
     <t>Tag</t>
@@ -94,7 +95,13 @@
     <t>Indirect Taxonomy</t>
   </si>
   <si>
-    <t>Indirect Beneficaries</t>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>Policy or Regulatory Framework</t>
+  </si>
+  <si>
+    <t>Policy Population</t>
   </si>
   <si>
     <t>Seventh Operational Phase of the GEF Small Grants Programme in Mexico</t>
@@ -103,7 +110,7 @@
     <t>https://open.undp.org/projects/00128385</t>
   </si>
   <si>
-    <t>Agricultural Services</t>
+    <t>Agriculture and Food System</t>
   </si>
   <si>
     <t>Project Specific Indicator 14: Number of community projects implementing renewable and energy-efficient technologies (with at least 40% of the projects with women’s participation)</t>
@@ -122,6 +129,12 @@
     <t>35%</t>
   </si>
   <si>
+    <t>Non-VF</t>
+  </si>
+  <si>
+    <t>Close the gap on energy access</t>
+  </si>
+  <si>
     <t>VF</t>
   </si>
   <si>
@@ -167,45 +180,57 @@
     <t>36%</t>
   </si>
   <si>
+    <t>Capacity Building Training</t>
+  </si>
+  <si>
+    <t>Planning project to design of communitaian energy services networks for support small farmers in Yucatán, México</t>
+  </si>
+  <si>
+    <t>70%</t>
+  </si>
+  <si>
+    <t>Planning project to asses the energy efficiency in Isla Arena, Campeche</t>
+  </si>
+  <si>
+    <t>62.5%</t>
+  </si>
+  <si>
+    <t>Transportation and E-mobility Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energy and technological transition to implement  outboard motors of tourism boats in Campeche </t>
+  </si>
+  <si>
+    <t>indirect beneficaries 30 (16 women, 14 men) potential</t>
+  </si>
+  <si>
+    <t>Women and youth entreprenurship, capacity strangthernig programmes and education programmes for energy transition in Quintana Roo</t>
+  </si>
+  <si>
+    <t>64%</t>
+  </si>
+  <si>
+    <t>indirect beneficiaries (154 (99 women, 55 men)</t>
+  </si>
+  <si>
+    <t>Planning project to asset the pontential of technological tranistion in motor taxis to implemtn electric motors in Uman, Yucatán.</t>
+  </si>
+  <si>
+    <t>100%</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Indirect Beneficaries</t>
+  </si>
+  <si>
+    <t>Agricultural Services</t>
+  </si>
+  <si>
     <t>Capacity Training</t>
   </si>
   <si>
-    <t>Planning project to design of communitaian energy services networks for support small farmers in Yucatán, México</t>
-  </si>
-  <si>
-    <t>70%</t>
-  </si>
-  <si>
-    <t>Planning project to asses the energy efficiency in Isla Arena, Campeche</t>
-  </si>
-  <si>
-    <t>62.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Energy and technological transition to implement  outboard motors of tourism boats in Campeche </t>
-  </si>
-  <si>
-    <t>indirect beneficaries 30 (16 women, 14 men) potential</t>
-  </si>
-  <si>
-    <t>Women and youth entreprenurship, capacity strangthernig programmes and education programmes for energy transition in Quintana Roo</t>
-  </si>
-  <si>
-    <t>64%</t>
-  </si>
-  <si>
-    <t>indirect beneficiaries (154 (99 women, 55 men)</t>
-  </si>
-  <si>
-    <t>Transport Services</t>
-  </si>
-  <si>
-    <t>Planning project to asset the pontential of technological tranistion in motor taxis to implemtn electric motors in Uman, Yucatán.</t>
-  </si>
-  <si>
-    <t>100%</t>
-  </si>
-  <si>
     <t>Comments</t>
   </si>
   <si>
@@ -243,6 +268,111 @@
   </si>
   <si>
     <t>14 dircet benefiaries (14 women)</t>
+  </si>
+  <si>
+    <t>Electricity Access</t>
+  </si>
+  <si>
+    <t>Number of people, disaggregated by sex, who gain access to clean electricity (direct access to electricity, lighting, cooling, etc.) </t>
+  </si>
+  <si>
+    <t>Energy (MW added)</t>
+  </si>
+  <si>
+    <t>Number of MW installed capacity</t>
+  </si>
+  <si>
+    <t>Clean Cooking</t>
+  </si>
+  <si>
+    <t>Number of people who gain access to clean cooking (direct access to clean cook stoves, clean fuels, biomass, etc.).</t>
+  </si>
+  <si>
+    <t>Clean Heating</t>
+  </si>
+  <si>
+    <t>Number of people who gain access to clean heating (direct access to clean electric heaters, clean fuels, etc.).</t>
+  </si>
+  <si>
+    <t>Number of people who gain access to clean, affordable, and sustainable electricity for agricultural and food system activities (direct access to power machines for crop, processing, milling, grinding, de-husking, pressing, canning, sealing and packaging electricity, heating, cooling, solar water pumping for irrigation etc.) </t>
+  </si>
+  <si>
+    <t>Health Services</t>
+  </si>
+  <si>
+    <t>Number of people who gain access to health care facilities (direct access to electricity and heating systems for clinics, hospitals, health centers etc.) </t>
+  </si>
+  <si>
+    <t>Water Services</t>
+  </si>
+  <si>
+    <t>Number of people who gain access to water services (powering water pumps, water distributions, waste management, etc.).  </t>
+  </si>
+  <si>
+    <t>Education Services</t>
+  </si>
+  <si>
+    <t>Number of people who gain access to education services through clean energy systems (including students, teachers, etc.) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of MJ saved from transport and e-mobility interventions (e.g., electric vehicles, charging stations, etc.)  </t>
+  </si>
+  <si>
+    <t>Energy Efficiency Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of MJ saved from energy efficiency interventions (e.g., building efficiency, industries, etc.)  </t>
+  </si>
+  <si>
+    <t>Energy Infrastructure Services</t>
+  </si>
+  <si>
+    <t>Number of people who benefits from energy infrastructure interventions (streetlight, transmission, and distribution lines, etc.) </t>
+  </si>
+  <si>
+    <t>Access to other service (electric vehicles, industries efficiency etc.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Financing support </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support for the development of market ecosystem </t>
+  </si>
+  <si>
+    <t>Medium Enterprises</t>
+  </si>
+  <si>
+    <t>Support for the development of medium enterprises in the energy transition market</t>
+  </si>
+  <si>
+    <t>Support for the development of small enterprises in the energy transition market</t>
+  </si>
+  <si>
+    <t>Number of people who benefits from training for enterprises on the energy business and energy finance. </t>
+  </si>
+  <si>
+    <t>Entrepreneurship Training</t>
+  </si>
+  <si>
+    <t>Training for enterprises on the energy business is assumed to result in at least 100 direct beneficiaries</t>
+  </si>
+  <si>
+    <t>Market Intervention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volume of investment (US dollars) leverage removing barriers to private and public investment in clean, reliable, affordable, and sustainable energy solutions and energy efficiency for social infrastructure, productive use of electricity and other services </t>
+  </si>
+  <si>
+    <t>Campaign Participant</t>
+  </si>
+  <si>
+    <t>Individuals who participate in advocacy and campaign on energy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of people supported by policy and regulatory framework development on clean, affordable, and sustainable energy </t>
+  </si>
+  <si>
+    <t>Any other type of beneficiary (please specify justification in Notes)</t>
   </si>
 </sst>
 </file>
@@ -252,12 +382,18 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -328,6 +464,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -349,7 +498,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -451,17 +600,6 @@
         <color rgb="FF000000"/>
       </left>
       <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
       <top/>
       <bottom/>
       <diagonal/>
@@ -490,137 +628,193 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -629,14 +823,29 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -953,16 +1162,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FB8CF27-2FE9-4C89-944F-63AF2575BE71}">
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:AE10"/>
   <sheetFormatPr defaultColWidth="19.5703125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="10" width="19.5703125" style="2"/>
+    <col min="1" max="7" width="19.5703125" style="2"/>
+    <col min="8" max="8" width="6.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="19.5703125" style="2"/>
     <col min="11" max="11" width="19.5703125" style="18"/>
-    <col min="12" max="13" width="19.5703125" style="7"/>
+    <col min="12" max="12" width="19.5703125" style="7"/>
+    <col min="13" max="13" width="4.28515625" style="7" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="19.5703125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:31">
       <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
@@ -990,406 +1202,571 @@
       <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="36" t="s">
+      <c r="J1" s="33" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="N1" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="O1" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="P1" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="8" t="s">
+      <c r="Q1" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="8" t="s">
+      <c r="R1" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="11" t="s">
+      <c r="S1" s="50" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:19" ht="183" customHeight="1">
-      <c r="A2" s="25">
+      <c r="T1" s="49" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="50" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" ht="321">
+      <c r="A2" s="38">
         <v>122398</v>
       </c>
-      <c r="B2" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="28" t="s">
-        <v>20</v>
+      <c r="B2" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="40" t="s">
+        <v>22</v>
       </c>
       <c r="D2" s="23">
         <v>50000</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H2" s="13">
         <v>163</v>
       </c>
-      <c r="I2" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" s="37" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" s="35" t="s">
+      <c r="I2" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="22" t="s">
+      <c r="J2" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="M2" s="14"/>
-      <c r="N2" s="16" t="s">
+      <c r="K2" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="O2" s="16" t="s">
+      <c r="L2" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="16"/>
-      <c r="R2" s="16"/>
-      <c r="S2" s="16" t="s">
+      <c r="M2" s="37"/>
+      <c r="N2" s="52" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="3" spans="1:19" ht="121.5">
-      <c r="A3" s="26"/>
-      <c r="B3" s="32"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="23">
+      <c r="O2" s="37"/>
+      <c r="P2" s="37"/>
+      <c r="Q2" s="37"/>
+      <c r="R2" s="37"/>
+      <c r="S2" s="53"/>
+      <c r="T2" s="37"/>
+      <c r="U2" s="53"/>
+      <c r="W2" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="X2" s="14"/>
+      <c r="Y2" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z2" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA2" s="37"/>
+      <c r="AB2" s="16"/>
+      <c r="AC2" s="16"/>
+      <c r="AD2" s="16"/>
+      <c r="AE2" s="16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" ht="121.5">
+      <c r="A3" s="25"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="42">
         <v>50000</v>
       </c>
-      <c r="E3" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="F3" s="19" t="s">
+      <c r="E3" s="43" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43">
+        <v>30</v>
+      </c>
+      <c r="I3" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="J3" s="34"/>
+      <c r="K3" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="L3" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" s="37"/>
+      <c r="N3" s="52" t="s">
+        <v>30</v>
+      </c>
+      <c r="O3" s="37"/>
+      <c r="P3" s="37"/>
+      <c r="Q3" s="37"/>
+      <c r="R3" s="37"/>
+      <c r="S3" s="53"/>
+      <c r="T3" s="37"/>
+      <c r="U3" s="53"/>
+      <c r="W3" s="22"/>
+      <c r="X3" s="14"/>
+      <c r="Y3" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13">
-        <v>30</v>
-      </c>
-      <c r="I3" s="34" t="s">
-        <v>33</v>
-      </c>
-      <c r="J3" s="38"/>
-      <c r="K3" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="L3" s="22"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="O3" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="P3" s="16"/>
-      <c r="Q3" s="16"/>
-      <c r="R3" s="16"/>
-      <c r="S3" s="16" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="91.5">
-      <c r="A4" s="26"/>
-      <c r="B4" s="32"/>
-      <c r="C4" s="29"/>
+      <c r="Z3" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA3" s="37"/>
+      <c r="AB3" s="16"/>
+      <c r="AC3" s="16"/>
+      <c r="AD3" s="16"/>
+      <c r="AE3" s="16" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" ht="91.5">
+      <c r="A4" s="25"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="27"/>
       <c r="D4" s="23">
         <v>4999</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G4" s="13"/>
       <c r="H4" s="13">
         <v>77</v>
       </c>
-      <c r="I4" s="34" t="s">
-        <v>37</v>
-      </c>
-      <c r="J4" s="38"/>
-      <c r="K4" s="35" t="s">
-        <v>38</v>
-      </c>
-      <c r="L4" s="22"/>
-      <c r="M4" s="14"/>
-      <c r="N4" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="O4" s="16" t="s">
+      <c r="I4" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" s="34"/>
+      <c r="K4" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="L4" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="P4" s="16"/>
-      <c r="Q4" s="16"/>
-      <c r="R4" s="16"/>
-      <c r="S4" s="16"/>
-    </row>
-    <row r="5" spans="1:19" ht="76.5">
-      <c r="A5" s="26"/>
-      <c r="B5" s="32"/>
-      <c r="C5" s="29"/>
+      <c r="M4" s="37"/>
+      <c r="N4" s="52" t="s">
+        <v>30</v>
+      </c>
+      <c r="O4" s="37"/>
+      <c r="P4" s="37"/>
+      <c r="Q4" s="37"/>
+      <c r="R4" s="37"/>
+      <c r="S4" s="53"/>
+      <c r="T4" s="37"/>
+      <c r="U4" s="53"/>
+      <c r="W4" s="22"/>
+      <c r="X4" s="14"/>
+      <c r="Y4" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z4" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA4" s="37"/>
+      <c r="AB4" s="16"/>
+      <c r="AC4" s="16"/>
+      <c r="AD4" s="16"/>
+      <c r="AE4" s="16"/>
+    </row>
+    <row r="5" spans="1:31" ht="76.5">
+      <c r="A5" s="25"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="27"/>
       <c r="D5" s="23">
         <v>4990</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G5" s="13"/>
       <c r="H5" s="13">
         <v>110</v>
       </c>
-      <c r="I5" s="34" t="s">
-        <v>40</v>
-      </c>
-      <c r="J5" s="38"/>
-      <c r="K5" s="35" t="s">
-        <v>41</v>
-      </c>
-      <c r="L5" s="22"/>
-      <c r="M5" s="14"/>
-      <c r="N5" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="O5" s="16" t="s">
+      <c r="I5" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="J5" s="34"/>
+      <c r="K5" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="L5" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="P5" s="16"/>
-      <c r="Q5" s="16"/>
-      <c r="R5" s="16"/>
-      <c r="S5" s="16"/>
-    </row>
-    <row r="6" spans="1:19" ht="106.5">
-      <c r="A6" s="26"/>
-      <c r="B6" s="32"/>
-      <c r="C6" s="29"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="52" t="s">
+        <v>30</v>
+      </c>
+      <c r="O5" s="37"/>
+      <c r="P5" s="37"/>
+      <c r="Q5" s="37"/>
+      <c r="R5" s="37"/>
+      <c r="S5" s="53"/>
+      <c r="T5" s="37"/>
+      <c r="U5" s="53"/>
+      <c r="W5" s="22"/>
+      <c r="X5" s="14"/>
+      <c r="Y5" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z5" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA5" s="37"/>
+      <c r="AB5" s="16"/>
+      <c r="AC5" s="16"/>
+      <c r="AD5" s="16"/>
+      <c r="AE5" s="16"/>
+    </row>
+    <row r="6" spans="1:31" ht="106.5">
+      <c r="A6" s="25"/>
+      <c r="B6" s="29"/>
+      <c r="C6" s="27"/>
       <c r="D6" s="23">
         <v>3992</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G6" s="13"/>
       <c r="H6" s="13">
         <v>402</v>
       </c>
-      <c r="I6" s="34" t="s">
-        <v>43</v>
-      </c>
-      <c r="J6" s="38"/>
-      <c r="K6" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="L6" s="22"/>
-      <c r="M6" s="14"/>
-      <c r="N6" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="O6" s="16" t="s">
+      <c r="I6" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="J6" s="34"/>
+      <c r="K6" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="L6" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="P6" s="16"/>
-      <c r="Q6" s="16"/>
-      <c r="R6" s="16"/>
-      <c r="S6" s="16"/>
-    </row>
-    <row r="7" spans="1:19" ht="60.75">
-      <c r="A7" s="26"/>
-      <c r="B7" s="32"/>
-      <c r="C7" s="29"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="52" t="s">
+        <v>30</v>
+      </c>
+      <c r="O6" s="37"/>
+      <c r="P6" s="37"/>
+      <c r="Q6" s="37"/>
+      <c r="R6" s="37"/>
+      <c r="S6" s="53"/>
+      <c r="T6" s="37"/>
+      <c r="U6" s="53"/>
+      <c r="W6" s="22"/>
+      <c r="X6" s="14"/>
+      <c r="Y6" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z6" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA6" s="37"/>
+      <c r="AB6" s="16"/>
+      <c r="AC6" s="16"/>
+      <c r="AD6" s="16"/>
+      <c r="AE6" s="16"/>
+    </row>
+    <row r="7" spans="1:31" ht="60.75">
+      <c r="A7" s="25"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="27"/>
       <c r="D7" s="23">
         <v>4997</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G7" s="13"/>
       <c r="H7" s="13">
         <v>400</v>
       </c>
-      <c r="I7" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="J7" s="38"/>
-      <c r="K7" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="L7" s="22"/>
-      <c r="M7" s="14"/>
-      <c r="N7" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="O7" s="16" t="s">
+      <c r="I7" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="J7" s="34"/>
+      <c r="K7" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="L7" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="P7" s="16"/>
-      <c r="Q7" s="16"/>
-      <c r="R7" s="16"/>
-      <c r="S7" s="16"/>
-    </row>
-    <row r="8" spans="1:19" ht="91.5">
-      <c r="A8" s="26"/>
-      <c r="B8" s="32"/>
-      <c r="C8" s="29"/>
+      <c r="M7" s="37"/>
+      <c r="N7" s="52" t="s">
+        <v>30</v>
+      </c>
+      <c r="O7" s="37"/>
+      <c r="P7" s="37"/>
+      <c r="Q7" s="37"/>
+      <c r="R7" s="37"/>
+      <c r="S7" s="53"/>
+      <c r="T7" s="37"/>
+      <c r="U7" s="53"/>
+      <c r="W7" s="22"/>
+      <c r="X7" s="14"/>
+      <c r="Y7" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z7" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA7" s="37"/>
+      <c r="AB7" s="16"/>
+      <c r="AC7" s="16"/>
+      <c r="AD7" s="16"/>
+      <c r="AE7" s="16"/>
+    </row>
+    <row r="8" spans="1:31" ht="91.5">
+      <c r="A8" s="25"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="27"/>
       <c r="D8" s="23">
         <v>50000</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13">
         <v>14</v>
       </c>
-      <c r="I8" s="34" t="s">
-        <v>47</v>
-      </c>
-      <c r="J8" s="38"/>
-      <c r="K8" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="L8" s="22"/>
-      <c r="M8" s="14"/>
-      <c r="N8" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="O8" s="16" t="s">
+      <c r="I8" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J8" s="34"/>
+      <c r="K8" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="L8" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="P8" s="16"/>
-      <c r="Q8" s="16"/>
-      <c r="R8" s="16"/>
-      <c r="S8" s="16" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" ht="137.25">
-      <c r="A9" s="26"/>
-      <c r="B9" s="32"/>
-      <c r="C9" s="29"/>
+      <c r="M8" s="37"/>
+      <c r="N8" s="52" t="s">
+        <v>30</v>
+      </c>
+      <c r="O8" s="37"/>
+      <c r="P8" s="37"/>
+      <c r="Q8" s="37"/>
+      <c r="R8" s="37"/>
+      <c r="S8" s="53"/>
+      <c r="T8" s="37"/>
+      <c r="U8" s="53"/>
+      <c r="W8" s="22"/>
+      <c r="X8" s="14"/>
+      <c r="Y8" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z8" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA8" s="37"/>
+      <c r="AB8" s="16"/>
+      <c r="AC8" s="16"/>
+      <c r="AD8" s="16"/>
+      <c r="AE8" s="16" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" ht="137.25">
+      <c r="A9" s="25"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="27"/>
       <c r="D9" s="23">
         <v>50000</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13">
         <v>14</v>
       </c>
-      <c r="I9" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="J9" s="38"/>
-      <c r="K9" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="L9" s="22"/>
-      <c r="M9" s="14"/>
-      <c r="N9" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="O9" s="16" t="s">
+      <c r="I9" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="J9" s="34"/>
+      <c r="K9" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="L9" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="P9" s="16"/>
-      <c r="Q9" s="16"/>
-      <c r="R9" s="16"/>
-      <c r="S9" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="106.5">
-      <c r="A10" s="27"/>
-      <c r="B10" s="33"/>
-      <c r="C10" s="30"/>
+      <c r="M9" s="37"/>
+      <c r="N9" s="52" t="s">
+        <v>30</v>
+      </c>
+      <c r="O9" s="37"/>
+      <c r="P9" s="37"/>
+      <c r="Q9" s="37"/>
+      <c r="R9" s="37"/>
+      <c r="S9" s="53"/>
+      <c r="T9" s="37"/>
+      <c r="U9" s="53"/>
+      <c r="W9" s="22"/>
+      <c r="X9" s="14"/>
+      <c r="Y9" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z9" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA9" s="37"/>
+      <c r="AB9" s="16"/>
+      <c r="AC9" s="16"/>
+      <c r="AD9" s="16"/>
+      <c r="AE9" s="16" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" ht="106.5">
+      <c r="A10" s="26"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="28"/>
       <c r="D10" s="23">
         <v>4900</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13">
         <v>15</v>
       </c>
-      <c r="I10" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="J10" s="39"/>
-      <c r="K10" s="35" t="s">
-        <v>54</v>
-      </c>
-      <c r="L10" s="22"/>
-      <c r="M10" s="14"/>
-      <c r="N10" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="O10" s="16" t="s">
+      <c r="I10" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="J10" s="35"/>
+      <c r="K10" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="L10" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="P10" s="16"/>
-      <c r="Q10" s="16"/>
-      <c r="R10" s="16"/>
-      <c r="S10" s="16"/>
+      <c r="M10" s="37"/>
+      <c r="N10" s="52" t="s">
+        <v>30</v>
+      </c>
+      <c r="O10" s="37"/>
+      <c r="P10" s="37"/>
+      <c r="Q10" s="37"/>
+      <c r="R10" s="37"/>
+      <c r="S10" s="53"/>
+      <c r="T10" s="37"/>
+      <c r="U10" s="53"/>
+      <c r="W10" s="22"/>
+      <c r="X10" s="14"/>
+      <c r="Y10" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z10" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA10" s="37"/>
+      <c r="AB10" s="16"/>
+      <c r="AC10" s="16"/>
+      <c r="AD10" s="16"/>
+      <c r="AE10" s="16"/>
     </row>
   </sheetData>
-  <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R10" xr:uid="{4B78D332-1485-4A2A-B8D4-10AA957FE2BD}">
+  <dataValidations count="13">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2:AD10" xr:uid="{4B78D332-1485-4A2A-B8D4-10AA957FE2BD}">
       <formula1>"Electricity Access, Energy Efficiency, Renewable EnergyEnergy Infrastructure,   Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q10" xr:uid="{1AA1A4BC-D39F-4894-BE62-DB60334617FE}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2:AC10 Q2:Q10" xr:uid="{1AA1A4BC-D39F-4894-BE62-DB60334617FE}">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P10" xr:uid="{F85F5BB7-E841-4EE2-B5A4-AB1F891F5256}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2:AB10" xr:uid="{F85F5BB7-E841-4EE2-B5A4-AB1F891F5256}">
       <formula1>" AMP, PUDC, Solar4Health, Action Opportunities, Italy UNDP Energy Partnership"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O10" xr:uid="{FD80936E-4835-4962-B0C8-215240FD0E55}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:Z10" xr:uid="{FD80936E-4835-4962-B0C8-215240FD0E55}">
       <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N10" xr:uid="{456A911B-0E42-4EBB-87AB-8F7318D0BA96}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y10 N2:N10" xr:uid="{456A911B-0E42-4EBB-87AB-8F7318D0BA96}">
       <formula1>"Accelerating just energy transition, Close the gap on energy access, Scale up energy finance"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA2:AA10" xr:uid="{574FBEC4-F4D1-456E-BE3F-A3CA83F84E52}">
+      <formula1>"Tier 1, Tier 2, Tier 3"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P10" xr:uid="{7FCBA540-EE41-4691-B84B-42934A1A0AFD}">
+      <formula1>"AMP, PUDC, Solar4Health, Action Opportunities, Italy UNDP Energy Partnership"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O10" xr:uid="{C72FBC00-846F-46E5-91B0-FF859A8608EA}">
+      <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy, Overall"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L10" xr:uid="{0FF9DF8F-273B-480C-A0C9-66CB6BD51E8F}">
+      <formula1>"Non-VF, VF"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M10" xr:uid="{6E72F0AA-E7D0-4234-928A-36C6773191C5}">
+      <formula1>"Finance, Gender, Efficiency, Just, Health"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T10" xr:uid="{9D429E18-B821-4D42-A827-57EDE4AB6B51}">
+      <formula1>"National, Regional, City, Community"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R10" xr:uid="{B4C33EDF-6E6F-49D3-AFE7-DB4B2D21C33F}">
+      <formula1>"Electricity Access, Energy Efficiency, Renewable Energy, Infrastructure,  Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid, Research &amp; Innovation, Grant &amp; Investment"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S10" xr:uid="{E16927F3-0721-4DBD-B128-1F14F81622E0}">
+      <formula1>"Solar, Wind, Bioenergy, Hydro, Geothermal, Waste, Some Sources, Other, Unknown"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -1397,6 +1774,18 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{40912E9C-520A-40CD-811A-4AA0A69A4FC2}">
+          <x14:formula1>
+            <xm:f>'Beneficiary Categories'!$A$2:$A$22</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E10</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -1446,13 +1835,13 @@
         <v>10</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="M1" s="8" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="11" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="O1" s="8" t="s">
         <v>13</v>
@@ -1475,45 +1864,45 @@
         <v>122398</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="42"/>
+        <v>21</v>
+      </c>
+      <c r="C2" s="56"/>
       <c r="D2" s="12">
         <v>50000</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H2" s="13">
         <v>163</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" s="41" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="J2" s="55" t="s">
+        <v>27</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="L2" s="40" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="L2" s="54" t="s">
+        <v>31</v>
       </c>
       <c r="M2" s="14"/>
       <c r="N2" s="16" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="O2" s="16" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="P2" s="16" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="Q2" s="16"/>
       <c r="R2" s="16"/>
@@ -1522,37 +1911,37 @@
     <row r="3" spans="1:19" ht="121.5">
       <c r="A3" s="20"/>
       <c r="B3" s="21"/>
-      <c r="C3" s="42"/>
+      <c r="C3" s="56"/>
       <c r="D3" s="12">
         <v>50000</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="13">
         <v>30</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="J3" s="41"/>
+        <v>37</v>
+      </c>
+      <c r="J3" s="55"/>
       <c r="K3" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="L3" s="40"/>
+        <v>38</v>
+      </c>
+      <c r="L3" s="54"/>
       <c r="M3" s="14"/>
       <c r="N3" s="16" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="O3" s="16" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="P3" s="16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="Q3" s="16"/>
       <c r="R3" s="16"/>
@@ -1561,35 +1950,35 @@
     <row r="4" spans="1:19" ht="91.5">
       <c r="A4" s="20"/>
       <c r="B4" s="21"/>
-      <c r="C4" s="42"/>
+      <c r="C4" s="56"/>
       <c r="D4" s="12">
         <v>4999</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G4" s="13"/>
       <c r="H4" s="13">
         <v>77</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="J4" s="41"/>
+        <v>41</v>
+      </c>
+      <c r="J4" s="55"/>
       <c r="K4" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L4" s="40"/>
+        <v>42</v>
+      </c>
+      <c r="L4" s="54"/>
       <c r="M4" s="14"/>
       <c r="N4" s="16"/>
       <c r="O4" s="16" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="P4" s="16" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="Q4" s="16"/>
       <c r="R4" s="16"/>
@@ -1598,35 +1987,35 @@
     <row r="5" spans="1:19" ht="76.5">
       <c r="A5" s="20"/>
       <c r="B5" s="21"/>
-      <c r="C5" s="42"/>
+      <c r="C5" s="56"/>
       <c r="D5" s="12">
         <v>4990</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G5" s="13"/>
       <c r="H5" s="13">
         <v>110</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="J5" s="41"/>
+        <v>44</v>
+      </c>
+      <c r="J5" s="55"/>
       <c r="K5" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="L5" s="40"/>
+        <v>45</v>
+      </c>
+      <c r="L5" s="54"/>
       <c r="M5" s="14"/>
       <c r="N5" s="16"/>
       <c r="O5" s="16" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="P5" s="16" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="Q5" s="16"/>
       <c r="R5" s="16"/>
@@ -1635,35 +2024,35 @@
     <row r="6" spans="1:19" ht="106.5">
       <c r="A6" s="20"/>
       <c r="B6" s="21"/>
-      <c r="C6" s="42"/>
+      <c r="C6" s="56"/>
       <c r="D6" s="12">
         <v>3992</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G6" s="13"/>
       <c r="H6" s="13">
         <v>402</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="J6" s="41"/>
+        <v>47</v>
+      </c>
+      <c r="J6" s="55"/>
       <c r="K6" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="L6" s="40"/>
+        <v>48</v>
+      </c>
+      <c r="L6" s="54"/>
       <c r="M6" s="14"/>
       <c r="N6" s="16"/>
       <c r="O6" s="16" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="P6" s="16" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="Q6" s="16"/>
       <c r="R6" s="16"/>
@@ -1672,35 +2061,35 @@
     <row r="7" spans="1:19" ht="60.75">
       <c r="A7" s="20"/>
       <c r="B7" s="21"/>
-      <c r="C7" s="42"/>
+      <c r="C7" s="56"/>
       <c r="D7" s="12">
         <v>4997</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G7" s="13"/>
       <c r="H7" s="13">
         <v>400</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="J7" s="41"/>
+        <v>49</v>
+      </c>
+      <c r="J7" s="55"/>
       <c r="K7" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="L7" s="40"/>
+        <v>50</v>
+      </c>
+      <c r="L7" s="54"/>
       <c r="M7" s="14"/>
       <c r="N7" s="16"/>
       <c r="O7" s="16" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="P7" s="16" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="Q7" s="16"/>
       <c r="R7" s="16"/>
@@ -1709,37 +2098,37 @@
     <row r="8" spans="1:19" ht="91.5">
       <c r="A8" s="20"/>
       <c r="B8" s="21"/>
-      <c r="C8" s="42"/>
+      <c r="C8" s="56"/>
       <c r="D8" s="12">
         <v>50000</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13">
         <v>14</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="J8" s="41"/>
+        <v>52</v>
+      </c>
+      <c r="J8" s="55"/>
       <c r="K8" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="L8" s="40"/>
+        <v>38</v>
+      </c>
+      <c r="L8" s="54"/>
       <c r="M8" s="14"/>
       <c r="N8" s="16" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="O8" s="16" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="P8" s="16" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="Q8" s="16"/>
       <c r="R8" s="16"/>
@@ -1748,37 +2137,37 @@
     <row r="9" spans="1:19" ht="137.25">
       <c r="A9" s="20"/>
       <c r="B9" s="21"/>
-      <c r="C9" s="42"/>
+      <c r="C9" s="56"/>
       <c r="D9" s="12">
         <v>50000</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13">
         <v>14</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="J9" s="41"/>
+        <v>54</v>
+      </c>
+      <c r="J9" s="55"/>
       <c r="K9" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="L9" s="40"/>
+        <v>55</v>
+      </c>
+      <c r="L9" s="54"/>
       <c r="M9" s="14"/>
       <c r="N9" s="16" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O9" s="16" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="P9" s="16" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="Q9" s="16"/>
       <c r="R9" s="16"/>
@@ -1787,35 +2176,35 @@
     <row r="10" spans="1:19" ht="106.5">
       <c r="A10" s="20"/>
       <c r="B10" s="21"/>
-      <c r="C10" s="42"/>
+      <c r="C10" s="56"/>
       <c r="D10" s="12">
         <v>4900</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13">
         <v>15</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="J10" s="41"/>
+        <v>57</v>
+      </c>
+      <c r="J10" s="55"/>
       <c r="K10" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="L10" s="40"/>
+        <v>58</v>
+      </c>
+      <c r="L10" s="54"/>
       <c r="M10" s="14"/>
       <c r="N10" s="16"/>
       <c r="O10" s="16" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="P10" s="16" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="Q10" s="16"/>
       <c r="R10" s="16"/>
@@ -1889,208 +2278,208 @@
         <v>9</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="183" customHeight="1">
-      <c r="A2" s="43">
+      <c r="A2" s="57">
         <v>122398</v>
       </c>
-      <c r="B2" s="45" t="s">
-        <v>19</v>
+      <c r="B2" s="59" t="s">
+        <v>21</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="6">
         <v>50000</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" s="47" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2" s="47" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2" s="47" t="s">
-        <v>56</v>
+        <v>61</v>
+      </c>
+      <c r="F2" s="61" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="61" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="61" t="s">
+        <v>64</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="J2" s="49" t="s">
-        <v>25</v>
+        <v>65</v>
+      </c>
+      <c r="J2" s="63" t="s">
+        <v>27</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="121.5">
-      <c r="A3" s="44"/>
-      <c r="B3" s="46"/>
+      <c r="A3" s="58"/>
+      <c r="B3" s="60"/>
       <c r="C3" s="3"/>
       <c r="D3" s="6">
         <v>50000</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
+        <v>67</v>
+      </c>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
       <c r="I3" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J3" s="49"/>
+        <v>37</v>
+      </c>
+      <c r="J3" s="63"/>
       <c r="K3" s="2" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="91.5">
-      <c r="A4" s="44"/>
-      <c r="B4" s="46"/>
+      <c r="A4" s="58"/>
+      <c r="B4" s="60"/>
       <c r="C4" s="3"/>
       <c r="D4" s="6">
         <v>4999</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
+        <v>61</v>
+      </c>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
       <c r="I4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J4" s="49"/>
+        <v>41</v>
+      </c>
+      <c r="J4" s="63"/>
       <c r="K4" s="2" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="76.5">
-      <c r="A5" s="44"/>
-      <c r="B5" s="46"/>
+      <c r="A5" s="58"/>
+      <c r="B5" s="60"/>
       <c r="C5" s="3"/>
       <c r="D5" s="6">
         <v>4990</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
+        <v>43</v>
+      </c>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
       <c r="I5" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J5" s="49"/>
+        <v>44</v>
+      </c>
+      <c r="J5" s="63"/>
       <c r="K5" s="2" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="106.5">
-      <c r="A6" s="44"/>
-      <c r="B6" s="46"/>
+      <c r="A6" s="58"/>
+      <c r="B6" s="60"/>
       <c r="C6" s="3"/>
       <c r="D6" s="6">
         <v>3992</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="48"/>
+        <v>62</v>
+      </c>
+      <c r="F6" s="62"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="62"/>
       <c r="I6" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="J6" s="49"/>
+        <v>47</v>
+      </c>
+      <c r="J6" s="63"/>
       <c r="K6" s="2" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="60.75">
-      <c r="A7" s="44"/>
-      <c r="B7" s="46"/>
+      <c r="A7" s="58"/>
+      <c r="B7" s="60"/>
       <c r="C7" s="3"/>
       <c r="D7" s="6">
         <v>4997</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F7" s="48"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="48"/>
+        <v>62</v>
+      </c>
+      <c r="F7" s="62"/>
+      <c r="G7" s="62"/>
+      <c r="H7" s="62"/>
       <c r="I7" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="J7" s="49"/>
+        <v>49</v>
+      </c>
+      <c r="J7" s="63"/>
       <c r="K7" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="91.5">
-      <c r="A8" s="44"/>
-      <c r="B8" s="46"/>
+      <c r="A8" s="58"/>
+      <c r="B8" s="60"/>
       <c r="C8" s="3"/>
       <c r="D8" s="6">
         <v>50000</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F8" s="48"/>
-      <c r="G8" s="48"/>
-      <c r="H8" s="48"/>
+        <v>35</v>
+      </c>
+      <c r="F8" s="62"/>
+      <c r="G8" s="62"/>
+      <c r="H8" s="62"/>
       <c r="I8" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="J8" s="49"/>
+        <v>52</v>
+      </c>
+      <c r="J8" s="63"/>
       <c r="K8" s="2" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="137.25">
-      <c r="A9" s="44"/>
-      <c r="B9" s="46"/>
+      <c r="A9" s="58"/>
+      <c r="B9" s="60"/>
       <c r="C9" s="3"/>
       <c r="D9" s="6">
         <v>50000</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="48"/>
+        <v>62</v>
+      </c>
+      <c r="F9" s="62"/>
+      <c r="G9" s="62"/>
+      <c r="H9" s="62"/>
       <c r="I9" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="J9" s="49"/>
+        <v>54</v>
+      </c>
+      <c r="J9" s="63"/>
       <c r="K9" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="106.5">
-      <c r="A10" s="44"/>
-      <c r="B10" s="46"/>
+      <c r="A10" s="58"/>
+      <c r="B10" s="60"/>
       <c r="C10" s="3"/>
       <c r="D10" s="6">
         <v>4900</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10" s="48"/>
-      <c r="G10" s="48"/>
-      <c r="H10" s="48"/>
+        <v>35</v>
+      </c>
+      <c r="F10" s="62"/>
+      <c r="G10" s="62"/>
+      <c r="H10" s="62"/>
       <c r="I10" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="J10" s="49"/>
+        <v>57</v>
+      </c>
+      <c r="J10" s="63"/>
       <c r="K10" s="2" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -2107,7 +2496,205 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62E5E596-E377-4D31-93FE-D35419D28F22}">
+  <dimension ref="A1:B22"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="2" width="52.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="46" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="45.75">
+      <c r="A2" s="64" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" s="47" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="64" t="s">
+        <v>78</v>
+      </c>
+      <c r="B3" s="47" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="30.75">
+      <c r="A4" s="64" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" s="47" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="30.75">
+      <c r="A5" s="64" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" s="47" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="91.5">
+      <c r="A6" s="64" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="47" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="45.75">
+      <c r="A7" s="64" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" s="47" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="45.75">
+      <c r="A8" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="B8" s="47" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="45.75">
+      <c r="A9" s="64" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" s="47" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="30.75">
+      <c r="A10" s="64" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="65" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="30.75">
+      <c r="A11" s="64" t="s">
+        <v>92</v>
+      </c>
+      <c r="B11" s="65" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="45.75">
+      <c r="A12" s="64" t="s">
+        <v>94</v>
+      </c>
+      <c r="B12" s="47" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="30.75">
+      <c r="A13" s="64" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="65" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="64" t="s">
+        <v>97</v>
+      </c>
+      <c r="B14" s="65" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="30.75">
+      <c r="A15" s="64" t="s">
+        <v>99</v>
+      </c>
+      <c r="B15" s="65" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="30.75">
+      <c r="A16" s="64" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="65" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="30.75">
+      <c r="A17" s="64" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="47" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="30.75">
+      <c r="A18" s="64" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" s="65" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="76.5">
+      <c r="A19" s="64" t="s">
+        <v>105</v>
+      </c>
+      <c r="B19" s="65" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="30.75">
+      <c r="A20" s="64" t="s">
+        <v>107</v>
+      </c>
+      <c r="B20" s="65" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="45.75">
+      <c r="A21" s="64" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="66" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="30.75">
+      <c r="A22" s="64" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" s="65" t="s">
+        <v>110</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
@@ -2116,15 +2703,6 @@
     <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2377,11 +2955,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54CB41BE-882E-42A9-B905-2DB3A3C09E48}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AEB4956-B0F7-4F9B-96FB-12F8150DB89F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AEB4956-B0F7-4F9B-96FB-12F8150DB89F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54CB41BE-882E-42A9-B905-2DB3A3C09E48}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/01_Input/00_CO Validation/Mexico - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Mexico - Energy Projects.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28224"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edgar.gonzalez\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="182" documentId="8_{F2D2D00D-A89C-0A4B-9B24-C268CBE6EBDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B4F09F7-6B93-41A4-96E8-93C2ECD02252}"/>
+  <xr:revisionPtr revIDLastSave="184" documentId="8_{F2D2D00D-A89C-0A4B-9B24-C268CBE6EBDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C68EFE72-D6A3-49A1-A48B-14D5A8E979E6}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2685" windowWidth="21600" windowHeight="11175" xr2:uid="{FE1040E1-1AC7-44EE-934B-383420C1C5D8}"/>
+    <workbookView xWindow="2685" yWindow="2685" windowWidth="21600" windowHeight="11175" firstSheet="3" activeTab="3" xr2:uid="{FE1040E1-1AC7-44EE-934B-383420C1C5D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects (3)" sheetId="3" r:id="rId1"/>
-    <sheet name="Projects (2)" sheetId="2" r:id="rId2"/>
-    <sheet name="Projects" sheetId="1" r:id="rId3"/>
+    <sheet name="Projects (2)" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="Projects" sheetId="1" state="hidden" r:id="rId3"/>
     <sheet name="Beneficiary Categories" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -2686,15 +2686,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
@@ -2705,9 +2696,9 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd25160c21e587dbb66203dfb8c7aa52">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05ccd5be12d50c438f9536854e894bcb" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
     <xsd:import namespace="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
     <xsd:element name="properties">
@@ -2732,6 +2723,7 @@
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -2811,6 +2803,11 @@
     <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -2954,14 +2951,23 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AEB4956-B0F7-4F9B-96FB-12F8150DB89F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54CB41BE-882E-42A9-B905-2DB3A3C09E48}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54CB41BE-882E-42A9-B905-2DB3A3C09E48}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7A8F006-9A76-4F0A-AC77-81DB00987992}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79DDB431-8A38-4936-93BD-B23A3B395CCC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AEB4956-B0F7-4F9B-96FB-12F8150DB89F}"/>
 </file>
--- a/01_Input/00_CO Validation/Mexico - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Mexico - Energy Projects.xlsx
@@ -302,7 +302,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -498,9 +498,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -586,6 +583,26 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>CO validation update</author>
+  </authors>
+  <commentList>
+    <comment ref="K11" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L11" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1676,15 +1693,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K11" s="13" t="n">
+      <c r="K11" s="68" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="68" t="n"/>
-      <c r="M11" s="69" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="M11" s="31" t="n"/>
       <c r="N11" s="35" t="n"/>
       <c r="O11" s="32" t="n"/>
       <c r="P11" s="37" t="n"/>
@@ -1707,7 +1720,7 @@
       <c r="AH11" s="16" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="16">
+  <dataValidations count="14">
     <dataValidation sqref="AD2:AD10" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Electricity Access, Energy Efficiency, Renewable EnergyEnergy Infrastructure,   Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid"</formula1>
     </dataValidation>
@@ -1750,18 +1763,13 @@
     <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
       <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1952,7 +1960,7 @@
     <row r="3" ht="121.5" customHeight="1">
       <c r="A3" s="20" t="n"/>
       <c r="B3" s="21" t="n"/>
-      <c r="C3" s="70" t="n"/>
+      <c r="C3" s="69" t="n"/>
       <c r="D3" s="12" t="n">
         <v>50000</v>
       </c>
@@ -1975,13 +1983,13 @@
           <t>Energy governance, gender inclusion and decision taken on off grid photovotaic systemt to support communitarian needs ofPunta allen, Quintana Roo</t>
         </is>
       </c>
-      <c r="J3" s="70" t="n"/>
+      <c r="J3" s="69" t="n"/>
       <c r="K3" s="54" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="L3" s="70" t="n"/>
+      <c r="L3" s="69" t="n"/>
       <c r="M3" s="14" t="n"/>
       <c r="N3" s="16" t="inlineStr">
         <is>
@@ -2005,7 +2013,7 @@
     <row r="4" ht="91.5" customHeight="1">
       <c r="A4" s="20" t="n"/>
       <c r="B4" s="21" t="n"/>
-      <c r="C4" s="70" t="n"/>
+      <c r="C4" s="69" t="n"/>
       <c r="D4" s="12" t="n">
         <v>4999</v>
       </c>
@@ -2028,13 +2036,13 @@
           <t>Planning project to design PV systems for solar pumps in indigenoud communities in Yucatán, México</t>
         </is>
       </c>
-      <c r="J4" s="70" t="n"/>
+      <c r="J4" s="69" t="n"/>
       <c r="K4" s="54" t="inlineStr">
         <is>
           <t>18%</t>
         </is>
       </c>
-      <c r="L4" s="70" t="n"/>
+      <c r="L4" s="69" t="n"/>
       <c r="M4" s="14" t="n"/>
       <c r="N4" s="16" t="n"/>
       <c r="O4" s="16" t="inlineStr">
@@ -2054,7 +2062,7 @@
     <row r="5" ht="76.5" customHeight="1">
       <c r="A5" s="20" t="n"/>
       <c r="B5" s="21" t="n"/>
-      <c r="C5" s="70" t="n"/>
+      <c r="C5" s="69" t="n"/>
       <c r="D5" s="12" t="n">
         <v>4990</v>
       </c>
@@ -2077,13 +2085,13 @@
           <t>Planning project to design PV systems for communitaian tourism enterprises in Yucatán, México</t>
         </is>
       </c>
-      <c r="J5" s="70" t="n"/>
+      <c r="J5" s="69" t="n"/>
       <c r="K5" s="54" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
       </c>
-      <c r="L5" s="70" t="n"/>
+      <c r="L5" s="69" t="n"/>
       <c r="M5" s="14" t="n"/>
       <c r="N5" s="16" t="n"/>
       <c r="O5" s="16" t="inlineStr">
@@ -2103,7 +2111,7 @@
     <row r="6" ht="106.5" customHeight="1">
       <c r="A6" s="20" t="n"/>
       <c r="B6" s="21" t="n"/>
-      <c r="C6" s="70" t="n"/>
+      <c r="C6" s="69" t="n"/>
       <c r="D6" s="12" t="n">
         <v>3992</v>
       </c>
@@ -2126,13 +2134,13 @@
           <t>Planning project to design of communitaian energy services networks for support small farmers in Yucatán, México</t>
         </is>
       </c>
-      <c r="J6" s="70" t="n"/>
+      <c r="J6" s="69" t="n"/>
       <c r="K6" s="54" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
       </c>
-      <c r="L6" s="70" t="n"/>
+      <c r="L6" s="69" t="n"/>
       <c r="M6" s="14" t="n"/>
       <c r="N6" s="16" t="n"/>
       <c r="O6" s="16" t="inlineStr">
@@ -2152,7 +2160,7 @@
     <row r="7" ht="60.75" customHeight="1">
       <c r="A7" s="20" t="n"/>
       <c r="B7" s="21" t="n"/>
-      <c r="C7" s="70" t="n"/>
+      <c r="C7" s="69" t="n"/>
       <c r="D7" s="12" t="n">
         <v>4997</v>
       </c>
@@ -2175,13 +2183,13 @@
           <t>Planning project to asses the energy efficiency in Isla Arena, Campeche</t>
         </is>
       </c>
-      <c r="J7" s="70" t="n"/>
+      <c r="J7" s="69" t="n"/>
       <c r="K7" s="54" t="inlineStr">
         <is>
           <t>62.5%</t>
         </is>
       </c>
-      <c r="L7" s="70" t="n"/>
+      <c r="L7" s="69" t="n"/>
       <c r="M7" s="14" t="n"/>
       <c r="N7" s="16" t="n"/>
       <c r="O7" s="16" t="inlineStr">
@@ -2201,7 +2209,7 @@
     <row r="8" ht="91.5" customHeight="1">
       <c r="A8" s="20" t="n"/>
       <c r="B8" s="21" t="n"/>
-      <c r="C8" s="70" t="n"/>
+      <c r="C8" s="69" t="n"/>
       <c r="D8" s="12" t="n">
         <v>50000</v>
       </c>
@@ -2224,13 +2232,13 @@
           <t xml:space="preserve">Energy and technological transition to implement  outboard motors of tourism boats in Campeche </t>
         </is>
       </c>
-      <c r="J8" s="70" t="n"/>
+      <c r="J8" s="69" t="n"/>
       <c r="K8" s="54" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="L8" s="70" t="n"/>
+      <c r="L8" s="69" t="n"/>
       <c r="M8" s="14" t="n"/>
       <c r="N8" s="16" t="inlineStr">
         <is>
@@ -2254,7 +2262,7 @@
     <row r="9" ht="137.25" customHeight="1">
       <c r="A9" s="20" t="n"/>
       <c r="B9" s="21" t="n"/>
-      <c r="C9" s="70" t="n"/>
+      <c r="C9" s="69" t="n"/>
       <c r="D9" s="12" t="n">
         <v>50000</v>
       </c>
@@ -2277,13 +2285,13 @@
           <t>Women and youth entreprenurship, capacity strangthernig programmes and education programmes for energy transition in Quintana Roo</t>
         </is>
       </c>
-      <c r="J9" s="70" t="n"/>
+      <c r="J9" s="69" t="n"/>
       <c r="K9" s="54" t="inlineStr">
         <is>
           <t>64%</t>
         </is>
       </c>
-      <c r="L9" s="70" t="n"/>
+      <c r="L9" s="69" t="n"/>
       <c r="M9" s="14" t="n"/>
       <c r="N9" s="16" t="inlineStr">
         <is>
@@ -2307,7 +2315,7 @@
     <row r="10" ht="106.5" customHeight="1">
       <c r="A10" s="20" t="n"/>
       <c r="B10" s="21" t="n"/>
-      <c r="C10" s="71" t="n"/>
+      <c r="C10" s="70" t="n"/>
       <c r="D10" s="12" t="n">
         <v>4900</v>
       </c>
@@ -2330,13 +2338,13 @@
           <t>Planning project to asset the pontential of technological tranistion in motor taxis to implemtn electric motors in Uman, Yucatán.</t>
         </is>
       </c>
-      <c r="J10" s="71" t="n"/>
+      <c r="J10" s="70" t="n"/>
       <c r="K10" s="54" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="L10" s="71" t="n"/>
+      <c r="L10" s="70" t="n"/>
       <c r="M10" s="14" t="n"/>
       <c r="N10" s="16" t="n"/>
       <c r="O10" s="16" t="inlineStr">
@@ -2695,288 +2703,288 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="72" t="inlineStr">
+      <c r="A1" s="71" t="inlineStr">
         <is>
           <t>Beneficiary Category</t>
         </is>
       </c>
-      <c r="B1" s="72" t="inlineStr">
+      <c r="B1" s="71" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
     </row>
     <row r="2" ht="45.75" customHeight="1">
-      <c r="A2" s="73" t="inlineStr">
+      <c r="A2" s="72" t="inlineStr">
         <is>
           <t>Electricity Access</t>
         </is>
       </c>
-      <c r="B2" s="73" t="inlineStr">
+      <c r="B2" s="72" t="inlineStr">
         <is>
           <t>Number of people, disaggregated by sex, who gain access to clean electricity (direct access to electricity, lighting, cooling, etc.).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="73" t="inlineStr">
+      <c r="A3" s="72" t="inlineStr">
         <is>
           <t>Energy (MW added)</t>
         </is>
       </c>
-      <c r="B3" s="73" t="inlineStr">
+      <c r="B3" s="72" t="inlineStr">
         <is>
           <t>Installed renewable or clean-energy power capacity added, in MW.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30.75" customHeight="1">
-      <c r="A4" s="73" t="inlineStr">
+      <c r="A4" s="72" t="inlineStr">
         <is>
           <t>Energy Storage (MW)</t>
         </is>
       </c>
-      <c r="B4" s="73" t="inlineStr">
+      <c r="B4" s="72" t="inlineStr">
         <is>
           <t>Installed energy storage power capacity added, in MW.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30.75" customHeight="1">
-      <c r="A5" s="73" t="inlineStr">
+      <c r="A5" s="72" t="inlineStr">
         <is>
           <t>Clean Cooking</t>
         </is>
       </c>
-      <c r="B5" s="73" t="inlineStr">
+      <c r="B5" s="72" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean cooking (direct access to clean cook stoves, clean fuels, biomass, etc.).</t>
         </is>
       </c>
     </row>
     <row r="6" ht="91.5" customHeight="1">
-      <c r="A6" s="73" t="inlineStr">
+      <c r="A6" s="72" t="inlineStr">
         <is>
           <t>Clean Heating</t>
         </is>
       </c>
-      <c r="B6" s="73" t="inlineStr">
+      <c r="B6" s="72" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean heating (direct access to clean electric heaters, clean fuels, etc.).</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45.75" customHeight="1">
-      <c r="A7" s="73" t="inlineStr">
+      <c r="A7" s="72" t="inlineStr">
         <is>
           <t>Agriculture and Food System</t>
         </is>
       </c>
-      <c r="B7" s="73" t="inlineStr">
+      <c r="B7" s="72" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean, affordable, and sustainable energy for agricultural and food-system activities.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="45.75" customHeight="1">
-      <c r="A8" s="73" t="inlineStr">
+      <c r="A8" s="72" t="inlineStr">
         <is>
           <t>Health Services</t>
         </is>
       </c>
-      <c r="B8" s="73" t="inlineStr">
+      <c r="B8" s="72" t="inlineStr">
         <is>
           <t>Number of people who gain access to health care facilities through clean energy systems.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="45.75" customHeight="1">
-      <c r="A9" s="73" t="inlineStr">
+      <c r="A9" s="72" t="inlineStr">
         <is>
           <t>Water Services</t>
         </is>
       </c>
-      <c r="B9" s="73" t="inlineStr">
+      <c r="B9" s="72" t="inlineStr">
         <is>
           <t>Number of people who gain access to water services through clean energy systems.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30.75" customHeight="1">
-      <c r="A10" s="73" t="inlineStr">
+      <c r="A10" s="72" t="inlineStr">
         <is>
           <t>Education Services</t>
         </is>
       </c>
-      <c r="B10" s="73" t="inlineStr">
+      <c r="B10" s="72" t="inlineStr">
         <is>
           <t>Number of people who gain access to education services through clean energy systems, including students and teachers.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30.75" customHeight="1">
-      <c r="A11" s="73" t="inlineStr">
+      <c r="A11" s="72" t="inlineStr">
         <is>
           <t>Transportation and E-mobility Services</t>
         </is>
       </c>
-      <c r="B11" s="73" t="inlineStr">
+      <c r="B11" s="72" t="inlineStr">
         <is>
           <t>Number of people served or energy saved from transport and e-mobility interventions, such as electric vehicles or charging stations.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="45.75" customHeight="1">
-      <c r="A12" s="73" t="inlineStr">
+      <c r="A12" s="72" t="inlineStr">
         <is>
           <t>Energy Efficiency Services</t>
         </is>
       </c>
-      <c r="B12" s="73" t="inlineStr">
+      <c r="B12" s="72" t="inlineStr">
         <is>
           <t>Energy saved from energy-efficiency interventions, such as building or industrial efficiency.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30.75" customHeight="1">
-      <c r="A13" s="73" t="inlineStr">
+      <c r="A13" s="72" t="inlineStr">
         <is>
           <t>Energy Infrastructure Services</t>
         </is>
       </c>
-      <c r="B13" s="73" t="inlineStr">
+      <c r="B13" s="72" t="inlineStr">
         <is>
           <t>Number of people benefiting from energy infrastructure interventions, such as streetlights, transmission, and distribution lines.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="73" t="inlineStr">
+      <c r="A14" s="72" t="inlineStr">
         <is>
           <t>Other Energy Services</t>
         </is>
       </c>
-      <c r="B14" s="73" t="inlineStr">
+      <c r="B14" s="72" t="inlineStr">
         <is>
           <t>Access to other energy services not captured by the categories above.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30.75" customHeight="1">
-      <c r="A15" s="73" t="inlineStr">
+      <c r="A15" s="72" t="inlineStr">
         <is>
           <t>Financing support</t>
         </is>
       </c>
-      <c r="B15" s="73" t="inlineStr">
+      <c r="B15" s="72" t="inlineStr">
         <is>
           <t>Support for the development of the energy market ecosystem.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30.75" customHeight="1">
-      <c r="A16" s="73" t="inlineStr">
+      <c r="A16" s="72" t="inlineStr">
         <is>
           <t>Medium Enterprises</t>
         </is>
       </c>
-      <c r="B16" s="73" t="inlineStr">
+      <c r="B16" s="72" t="inlineStr">
         <is>
           <t>Support for the development of medium enterprises in the energy transition market.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30.75" customHeight="1">
-      <c r="A17" s="73" t="inlineStr">
+      <c r="A17" s="72" t="inlineStr">
         <is>
           <t>Small Enterprises</t>
         </is>
       </c>
-      <c r="B17" s="73" t="inlineStr">
+      <c r="B17" s="72" t="inlineStr">
         <is>
           <t>Support for the development of small enterprises in the energy transition market.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30.75" customHeight="1">
-      <c r="A18" s="73" t="inlineStr">
+      <c r="A18" s="72" t="inlineStr">
         <is>
           <t>Capacity Building Training</t>
         </is>
       </c>
-      <c r="B18" s="73" t="inlineStr">
+      <c r="B18" s="72" t="inlineStr">
         <is>
           <t>Number of people benefiting from training on energy business, energy finance, or related implementation capacity.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="76.5" customHeight="1">
-      <c r="A19" s="73" t="inlineStr">
+      <c r="A19" s="72" t="inlineStr">
         <is>
           <t>Entrepreneurship Training</t>
         </is>
       </c>
-      <c r="B19" s="73" t="inlineStr">
+      <c r="B19" s="72" t="inlineStr">
         <is>
           <t>Training for enterprises on the energy business, assumed to result in direct beneficiaries.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30.75" customHeight="1">
-      <c r="A20" s="73" t="inlineStr">
+      <c r="A20" s="72" t="inlineStr">
         <is>
           <t>Market Intervention</t>
         </is>
       </c>
-      <c r="B20" s="73" t="inlineStr">
+      <c r="B20" s="72" t="inlineStr">
         <is>
           <t>Volume of investment leveraged or barriers removed for clean, reliable, affordable, and sustainable energy solutions.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="45.75" customHeight="1">
-      <c r="A21" s="73" t="inlineStr">
+      <c r="A21" s="72" t="inlineStr">
         <is>
           <t>Campaign Participant</t>
         </is>
       </c>
-      <c r="B21" s="73" t="inlineStr">
+      <c r="B21" s="72" t="inlineStr">
         <is>
           <t>Individuals who participate in advocacy or awareness campaigns on energy.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30.75" customHeight="1">
-      <c r="A22" s="73" t="inlineStr">
+      <c r="A22" s="72" t="inlineStr">
         <is>
           <t>Policy or Regulatory Framework</t>
         </is>
       </c>
-      <c r="B22" s="73" t="inlineStr">
+      <c r="B22" s="72" t="inlineStr">
         <is>
           <t>Policies, regulations, strategies, plans, or frameworks developed, approved, implemented, or strengthened.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="73" t="inlineStr">
+      <c r="A23" s="72" t="inlineStr">
         <is>
           <t>GHG Emissions Reduction</t>
         </is>
       </c>
-      <c r="B23" s="73" t="inlineStr">
+      <c r="B23" s="72" t="inlineStr">
         <is>
           <t>Greenhouse gas emissions reduced or mitigated, in tCO2e.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="73" t="inlineStr">
+      <c r="A24" s="72" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B24" s="73" t="inlineStr">
+      <c r="B24" s="72" t="inlineStr">
         <is>
           <t>Energy-related output that does not fit the standard categories above.</t>
         </is>
